--- a/MI_matrix_scen1.xlsx
+++ b/MI_matrix_scen1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A76797C-D534-7B42-A98E-878D65BA1F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{5A76797C-D534-7B42-A98E-878D65BA1F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A555F1-AA07-49E2-BFBE-0C77DE34F696}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="2000" windowWidth="26840" windowHeight="15440" xr2:uid="{5398184B-77C5-6841-9F4F-75A0837DFA33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{5398184B-77C5-6841-9F4F-75A0837DFA33}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ark2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>concrete</t>
   </si>
@@ -124,6 +125,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,9 +449,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F03A94D-68C2-8049-B735-E35B6092DFFB}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -472,11 +477,163 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
+        <v>812.11500000000001</v>
+      </c>
+      <c r="C2">
+        <v>451.17500000000001</v>
+      </c>
+      <c r="D2">
+        <v>451.17500000000001</v>
+      </c>
+      <c r="E2">
+        <v>83.049184073107057</v>
+      </c>
+      <c r="F2">
+        <v>4.8298107049608348</v>
+      </c>
+      <c r="G2">
+        <v>2.356005221932115</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1804.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>553.18499999999995</v>
+      </c>
+      <c r="C3">
+        <v>307.32499999999999</v>
+      </c>
+      <c r="D3">
+        <v>307.32499999999999</v>
+      </c>
+      <c r="E3">
+        <v>48.365901639344266</v>
+      </c>
+      <c r="F3">
+        <v>2.0152459016393447</v>
+      </c>
+      <c r="G3">
+        <v>2.0152459016393447</v>
+      </c>
+      <c r="H3">
+        <v>9.0686065573770502</v>
+      </c>
+      <c r="I3">
+        <v>1229.3000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>812.11500000000001</v>
+      </c>
+      <c r="C4">
+        <v>451.17500000000001</v>
+      </c>
+      <c r="D4">
+        <v>451.17500000000001</v>
+      </c>
+      <c r="E4">
+        <v>83.049184073107057</v>
+      </c>
+      <c r="F4">
+        <v>4.8298107049608348</v>
+      </c>
+      <c r="G4">
+        <v>2.356005221932115</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1804.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>555.16499999999996</v>
+      </c>
+      <c r="C5">
+        <v>308.42500000000001</v>
+      </c>
+      <c r="D5">
+        <v>308.42500000000001</v>
+      </c>
+      <c r="E5">
+        <v>53.878392116182575</v>
+      </c>
+      <c r="F5">
+        <v>3.8393153526970951</v>
+      </c>
+      <c r="G5">
+        <v>3.7113381742738589</v>
+      </c>
+      <c r="H5">
+        <v>0.25595435684647305</v>
+      </c>
+      <c r="I5">
+        <v>1233.6999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8102DB-C6A9-4AF1-892F-FE6358FDF272}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
         <v>360.94</v>
       </c>
       <c r="C2">
@@ -501,7 +658,7 @@
         <v>1804.7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -530,7 +687,7 @@
         <v>1229.3000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -559,7 +716,7 @@
         <v>1804.7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
